--- a/projects/QNL/QNL_Assumption_Log.xlsx
+++ b/projects/QNL/QNL_Assumption_Log.xlsx
@@ -674,7 +674,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="8.21875" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1510,12 +1510,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>78 system/aggregate telemetry tags (CHW plant instrumentation 21, electrical metering 24, DX group/staging 11, CCU room sensors 10, misc 12)</t>
+          <t>68 system/aggregate telemetry tags (CHW plant instrumentation 21, electrical metering 24, DX group/staging 11, misc 12)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>In the historian and Selected sheet under a family prefix, but each is a single building- or system-level measurement, not an equipment unit (e.g. CHW_BldgAvgSupTemp, ELEC_MFM_MVP1, DX_RP21 staging, CCU_AVServerRmHumd)</t>
+          <t>In the historian and Selected sheet under a family prefix, but each is a single building- or system-level measurement, not tied to any register unit (e.g. CHW_BldgAvgSupTemp, ELEC_MFM_MVP1, DX_RP21 staging, TotalEnergy)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1525,12 +1525,59 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>These are points that need a parent entity - the chilled-water loop/system, the electrical system, or specific units - which the sources do not settle. Modelling them as standalone equipment would invent units that do not exist. Held for the client to direct where they attach.</t>
+          <t>These are points whose equipment parent is unknown, or building-level points with no equipment. Per the client, such points either attach to their equipment or, if none, to the building - to be confirmed per group before modelling. Held pending that direction.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
           <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>QNL-025</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Points</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>10 CCU room sensors (CCU_AVServerRm/MDFRm/QTelRm/ServerRm Humd &amp; Temp)</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Selected + historian, named under the CCU prefix but not tied to any register CCU unit</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Modelled each as its measurement class (brick:Relative_Humidity_Sensor / brick:Temperature_Sensor), brick:isPartOf entity:HVAC, with its timeseries and unit, but NO rec:locatedIn</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Client directed: treat as orphans like the register-absent units, do not assume they belong to the register CCUs that share those rooms. The tag is the sensor itself, so it is the point; its equipment parent is unknown, so only HVAC-system membership is asserted.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
     </row>

--- a/projects/QNL/QNL_Assumption_Log.xlsx
+++ b/projects/QNL/QNL_Assumption_Log.xlsx
@@ -674,7 +674,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="8.21875" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1520,17 +1520,17 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>NOT modelled this pass</t>
+          <t>Modelled each against the parent its Dar Cairo / SSC counterpart uses: CHW plant instrumentation -&gt; the chilled-water loop entity:QNL_CHWS-MAIN-LOOP, with a brick:Building_Chilled_Water_Meter sub-part for the energy points (Dar Cairo's CHWS-MAIN-LOOP_Energy-Meter shape); electrical metering -&gt; one brick:Electrical_Meter per meter under entity:Electrical_System, plus para:Utility_Meter for the building total; DX_RP21 and CR_DX_EWRC500 -&gt; orphan para:DXUnit isPartOf HVAC (roof/control DX the register omits); loose room sensors and group statuses/setpoints -&gt; orphan points isPartOf HVAC. Elec_Gen_ACB3 -&gt; a breaker part of the generator.</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>These are points whose equipment parent is unknown, or building-level points with no equipment. Per the client, such points either attach to their equipment or, if none, to the building - to be confirmed per group before modelling. Held pending that direction.</t>
+          <t>Priority Dar Cairo -&gt; Brick -&gt; SSC. Dar Cairo hangs loop temps/flows/pressures on the loop and energy on a Building_Chilled_Water_Meter; both Dar Cairo (1,456) and SSC (46) model electrical measurement as brick:Electrical_Meter entities carrying power/energy points. Orphan DX units and loose points follow the CCU-orphan rule: class + HVAC membership, no location.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>292</t>
         </is>
       </c>
     </row>
@@ -1578,6 +1578,53 @@
       <c r="I19" t="inlineStr">
         <is>
           <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>QNL-026</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Class</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Points</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>3 new para: point/meter classes</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>para:Required_Units_Count, para:Stage_Up_Delay_Setpoint (DX_RP21 staging); para:Utility_Meter (building total energy)</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Coined as owl:Class under their closest Brick parent (brick:Point / brick:Setpoint / brick:Electrical_Meter)</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>No Dar Cairo, Brick 1.4 or SSC term exists for a DX required-units count, a stage-up delay, or a building utility meter (para:Utility_Meter reuses Dar Cairo's own name and parent).</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
     </row>
